--- a/Test_Data/DimSchedule.xlsx
+++ b/Test_Data/DimSchedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55cd0139eebd0c53/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55cd0139eebd0c53/Desktop/Github Repo/PaupackLaxStatTracking/Test_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A57E856F-5E94-46A2-BFC7-6C0CCD06CE03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{A57E856F-5E94-46A2-BFC7-6C0CCD06CE03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EF1FCD3-1CD7-4F1E-9D38-38D6DB3D08DD}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5010" windowWidth="29040" windowHeight="15720" xr2:uid="{5BB70DB8-0B8D-4C6D-8574-C9CE147F1544}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{5BB70DB8-0B8D-4C6D-8574-C9CE147F1544}"/>
   </bookViews>
   <sheets>
     <sheet name="DimSchedule" sheetId="2" r:id="rId1"/>

--- a/Test_Data/DimSchedule.xlsx
+++ b/Test_Data/DimSchedule.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55cd0139eebd0c53/Desktop/Github Repo/PaupackLaxStatTracking/Test_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{A57E856F-5E94-46A2-BFC7-6C0CCD06CE03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EF1FCD3-1CD7-4F1E-9D38-38D6DB3D08DD}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="8_{A57E856F-5E94-46A2-BFC7-6C0CCD06CE03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00DB7C8B-897F-4851-8F0B-AB9678A0AB93}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{5BB70DB8-0B8D-4C6D-8574-C9CE147F1544}"/>
+    <workbookView xWindow="57480" yWindow="-5010" windowWidth="29040" windowHeight="15720" xr2:uid="{5BB70DB8-0B8D-4C6D-8574-C9CE147F1544}"/>
   </bookViews>
   <sheets>
     <sheet name="DimSchedule" sheetId="2" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DimSchedule!$A$1:$O$8</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -135,7 +138,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -152,6 +158,13 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -198,10 +211,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -212,9 +226,11 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -227,6 +243,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -546,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49C65C0B-D46B-48CD-B08E-AD5E50463B16}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -942,7 +962,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="E11" s="4"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="E12" s="4"/>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:O8" xr:uid="{49C65C0B-D46B-48CD-B08E-AD5E50463B16}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O8">
+      <sortCondition ref="A1:A8"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Test_Data/DimSchedule.xlsx
+++ b/Test_Data/DimSchedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55cd0139eebd0c53/Desktop/Github Repo/PaupackLaxStatTracking/Test_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{A57E856F-5E94-46A2-BFC7-6C0CCD06CE03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00DB7C8B-897F-4851-8F0B-AB9678A0AB93}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="8_{A57E856F-5E94-46A2-BFC7-6C0CCD06CE03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50D7F2F3-C6E2-4AC7-A48A-4A50ED5AE888}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-5010" windowWidth="29040" windowHeight="15720" xr2:uid="{5BB70DB8-0B8D-4C6D-8574-C9CE147F1544}"/>
+    <workbookView xWindow="28680" yWindow="-5010" windowWidth="29040" windowHeight="15720" xr2:uid="{5BB70DB8-0B8D-4C6D-8574-C9CE147F1544}"/>
   </bookViews>
   <sheets>
     <sheet name="DimSchedule" sheetId="2" r:id="rId1"/>
